--- a/B911306_송범규_Use_Case_Description.xlsx
+++ b/B911306_송범규_Use_Case_Description.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BK_\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BK_\Documents\GitHub\SW_engineering_HW2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FFEF85-74F4-4F3D-B9C3-AD37B2ACA592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19F6C3A-5E0D-463E-AAE4-FCEB4F9D88A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>Use Case Description</t>
   </si>
@@ -53,26 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. 회원가입 메뉴를 누른다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. 회원가입 입력 양식을 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. 로그인 메뉴를 누른다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5. 사용자 ID와 비밀번호를 입력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>로그인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -81,23 +61,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7. 로그아웃 메뉴를 누른다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>자전거 등록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7. 자전거 등록 메뉴를 누른다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7. 현재 대여중인 자전거 조회 메뉴를 누른다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9. 자전거 ID, 자전거 제품명을 입력한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -105,63 +69,67 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>7. 회원이 자전거 대여 버튼을 클릭한다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>대여중인 자전거 리스트 조회</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>2. 로그인, 회원 가입 메뉴를 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. 가입완료 메시지 출력. 로그인, 회원 가입 메뉴를 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. 로그인 화면을 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. 사용자에 따른 메뉴를 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. 로그아웃 메시지 출력, 로그인, 회원 가입 메뉴를 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. 관리자용 메뉴를 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. 자전거 등록 화면을 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10. 자전거가 등록되었다는 메시지를 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. 회원용 메뉴를 출력한다.</t>
+    <t>1. 회원은 회원가입 메뉴 번호와 ID, 비밀번호, 전화번호를 입력한다.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>10. 대여 완료 되었다는 메시지를 출력한다.</t>
+    <t>2. 회원가입 메뉴 번호와 메뉴명을 출력한다. 그 다음줄에 회원이 입력한 ID, 비밀번호, 전화번호를 입력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 사용자는 로그인 메뉴번호와 ID와 비밀번호를 입력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 사용자는 로그아웃 메뉴 번호를 입력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 관리자는 자전거 등록 메뉴 번호와 자전거 ID, 자전거 제품명을 입력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 로그인 메뉴 번호와 메뉴명을 출력한다. 그 다음줄에 사용자가 입력한 ID, 비밀번호를 출력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 로그아웃 메뉴 번호와 메뉴명을 출력한다. 그 다음줄에 사용자의 ID를 출력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 회원은 자전거 대여 메뉴 번호와 자전거 ID를 입력한다.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>6. 회원용 메뉴를 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8. 회원이 대여중인 자전거 리스트를 출력한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5. 사용자가 ID, 비밀번호, 전화번호를 입력 후 가입 버튼을 누른다.</t>
+    <t>2. 자전거 대여 메뉴 번호와 메뉴명을 출력한다. 그 다음줄에 회원이 대여한 자전거 ID, 자전거 제품명을 출력한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 자전거 등록 메뉴 번호와 메뉴명을 출력한다. 그 다음줄에 관리자가 등록한 자전거 ID, 자전거 제품명을 출력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 회원은 현재 대여중인 자전거 조회 메뉴 번호를 입력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 대여 리스트 메뉴 번호와 메뉴명을 출력한다. 그 다음줄에 회원이 대여중인 자전거 ID, 자전거 제품명 리스트를 출력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시스템 종료</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 사용자는 시스템 종료 메뉴 번호를 입력한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 시스템 종료 메뉴 번호와 메뉴명을 출력한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -262,7 +230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -287,19 +255,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -313,11 +268,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -325,21 +310,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -349,31 +327,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -713,7 +703,7 @@
   <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.875" customWidth="1"/>
+    <col min="1" max="1" width="44.125" customWidth="1"/>
     <col min="2" max="2" width="50.375" customWidth="1"/>
     <col min="3" max="3" width="47.5" customWidth="1"/>
     <col min="4" max="4" width="42.25" customWidth="1"/>
@@ -721,308 +711,207 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12"/>
+      <c r="B3" s="9"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:2" ht="27" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B7" s="9"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="27" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="9"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="27" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="9"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="B25" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="12"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="20"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B28" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="13" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="12"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="17" t="s">
+      <c r="B29" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="12"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="12"/>
-    </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>3</v>
-      </c>
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>19</v>
-      </c>
       <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>21</v>
-      </c>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>27</v>
-      </c>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>28</v>
-      </c>
       <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="6"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" s="10"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>30</v>
-      </c>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
@@ -1104,13 +993,9 @@
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-    </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="7"/>
-      <c r="B71" s="8"/>
+      <c r="A71" s="1"/>
+      <c r="B71" s="2"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
@@ -1136,13 +1021,9 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-    </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="7"/>
-      <c r="B79" s="8"/>
+      <c r="A79" s="1"/>
+      <c r="B79" s="2"/>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
@@ -1168,13 +1049,9 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-    </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="7"/>
-      <c r="B87" s="8"/>
+      <c r="A87" s="1"/>
+      <c r="B87" s="2"/>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
@@ -1201,7 +1078,6 @@
       <c r="B93" s="4"/>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="6"/>
       <c r="B94" s="4"/>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -1241,13 +1117,9 @@
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-    </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" s="7"/>
-      <c r="B127" s="8"/>
+      <c r="A127" s="1"/>
+      <c r="B127" s="2"/>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
@@ -1269,13 +1141,9 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-    </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" s="7"/>
-      <c r="B134" s="8"/>
+      <c r="A134" s="1"/>
+      <c r="B134" s="2"/>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
@@ -1301,13 +1169,9 @@
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-    </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" s="7"/>
-      <c r="B142" s="8"/>
+      <c r="A142" s="1"/>
+      <c r="B142" s="2"/>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
@@ -1317,13 +1181,9 @@
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-    </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" s="7"/>
-      <c r="B146" s="8"/>
+      <c r="A146" s="1"/>
+      <c r="B146" s="2"/>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
@@ -1333,13 +1193,9 @@
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-    </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A150" s="7"/>
-      <c r="B150" s="8"/>
+      <c r="A150" s="1"/>
+      <c r="B150" s="2"/>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
@@ -1369,13 +1225,9 @@
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
-    </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="7"/>
-      <c r="B159" s="8"/>
+      <c r="A159" s="1"/>
+      <c r="B159" s="2"/>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
